--- a/resumes.xlsx
+++ b/resumes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jmangroupltd-my.sharepoint.com/personal/fahmida_jmangroup_com/Documents/Desktop/Jhire_agent/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_23F921ED3F334E1F1D2D4C9E35AA7235646CBEE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D291A81A-5A94-4D17-952B-BDA71F7001A7}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_23F921ED3F334E1F1D2D4C9E35AA7235646CBEE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B054E640-00E7-485B-9CA2-1B28B96C7246}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -764,10 +764,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="12" max="12" width="46.85546875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="51.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
